--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487427_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487427_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5869</v>
+        <v>5.1091</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3028</v>
+        <v>1.2795</v>
       </c>
       <c r="F2" t="n">
-        <v>4.284</v>
+        <v>3.8296</v>
       </c>
       <c r="G2" t="n">
         <v>2.6981</v>
@@ -610,13 +610,13 @@
         <v>3.5253</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5754</v>
+        <v>1.0976</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4815</v>
+        <v>0.4581</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0939</v>
+        <v>0.6395</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0576</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1593</v>
+        <v>4.7441</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1351</v>
+        <v>1.9071</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0241</v>
+        <v>2.837</v>
       </c>
       <c r="G3" t="n">
         <v>2.2826</v>
@@ -688,13 +688,13 @@
         <v>3.917</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8595</v>
+        <v>1.4443</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3419</v>
+        <v>1.1139</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5175</v>
+        <v>0.3304</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9412</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4737</v>
+        <v>2.825</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0033</v>
+        <v>0.515</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4704</v>
+        <v>2.31</v>
       </c>
       <c r="G4" t="n">
         <v>2.2829</v>
@@ -766,13 +766,13 @@
         <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1422</v>
+        <v>0.2091</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6534</v>
+        <v>-0.1417</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5112</v>
+        <v>0.3508</v>
       </c>
       <c r="V4" t="n">
         <v>0.3329</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5831</v>
+        <v>2.4291</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1136</v>
+        <v>0.1192</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4694</v>
+        <v>2.3098</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8004</v>
+        <v>-0.2878</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7962</v>
+        <v>-2.541</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5966</v>
+        <v>2.2532</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3347</v>
+        <v>0.0341</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2891</v>
+        <v>-1.3901</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0456</v>
+        <v>1.4242</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5344</v>
+        <v>-0.3219</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0853</v>
+        <v>-1.151</v>
       </c>
       <c r="O5" t="n">
-        <v>0.551</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1543</v>
+        <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8844</v>
+        <v>-0.8119</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9504</v>
+        <v>-0.2317</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06610000000000001</v>
+        <v>-0.5802</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3329</v>
+        <v>2.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8837</v>
+        <v>1.492</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2166</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5431</v>
+        <v>2.0191</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3925</v>
+        <v>1.523</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9356</v>
+        <v>0.4962</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2878</v>
+        <v>2.8004</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.541</v>
+        <v>-0.7962</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2532</v>
+        <v>3.5966</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0341</v>
+        <v>3.3347</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3901</v>
+        <v>0.2891</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4242</v>
+        <v>3.0456</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3219</v>
+        <v>-0.5344</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.151</v>
+        <v>-1.0853</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R6" t="n">
-        <v>2.546</v>
+        <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6978</v>
+        <v>-0.4483</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.5411</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9544</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1578</v>
+        <v>-0.3329</v>
       </c>
       <c r="W6" t="n">
-        <v>1.492</v>
+        <v>0.8837</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6659</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3398</v>
+        <v>0.4246</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5006</v>
+        <v>-2.0375</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1608</v>
+        <v>2.4621</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2647</v>
+        <v>-0.8141</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5992</v>
+        <v>0.1514</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8639</v>
+        <v>-0.9655</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2022</v>
+        <v>0.189</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.242</v>
+        <v>1.9836</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4442</v>
+        <v>-1.7946</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9375</v>
+        <v>-1.0031</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3572</v>
+        <v>-1.8322</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4197</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1751</v>
+        <v>-2.9377</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3709</v>
+        <v>4.1128</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1784</v>
+        <v>0.1212</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4734</v>
+        <v>0.4934</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6518</v>
+        <v>-0.3723</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0576</v>
+        <v>-0.0576</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0576</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0244</v>
+        <v>-0.0963</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6515</v>
+        <v>0.0912</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6759</v>
+        <v>-0.1875</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8141</v>
+        <v>0.2647</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1514</v>
+        <v>-2.5992</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9655</v>
+        <v>2.8639</v>
       </c>
       <c r="J8" t="n">
-        <v>0.189</v>
+        <v>1.2022</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9836</v>
+        <v>-1.242</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7946</v>
+        <v>2.4442</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0031</v>
+        <v>-0.9375</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8322</v>
+        <v>-1.3572</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.4197</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9377</v>
+        <v>-1.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>4.1128</v>
+        <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.279</v>
+        <v>-0.6145</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1206</v>
+        <v>0.0641</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1584</v>
+        <v>-0.6786</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0576</v>
+        <v>0.0576</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2178</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2754</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9183</v>
+        <v>-0.5044</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6144</v>
+        <v>-1.3074</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8684</v>
@@ -1156,13 +1156,13 @@
         <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.1441</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>-0.0494</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2016</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0.3329</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2132</v>
+        <v>-1.2796</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4908</v>
+        <v>-2.7978</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2776</v>
+        <v>1.5182</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2975</v>
@@ -1234,13 +1234,13 @@
         <v>3.5253</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8297</v>
+        <v>0.7632</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9181</v>
+        <v>0.6111</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08840000000000001</v>
+        <v>0.1522</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3329</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9759</v>
+        <v>-2.2015</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.323</v>
+        <v>0.291</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6529</v>
+        <v>-2.4925</v>
       </c>
       <c r="G11" t="n">
         <v>0.3296</v>
@@ -1312,13 +1312,13 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8516</v>
+        <v>-1.0772</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.188</v>
+        <v>-0.574</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6635</v>
+        <v>-0.5031</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4332</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6244</v>
+        <v>-3.4908</v>
       </c>
       <c r="E12" t="n">
         <v>-0.9247</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6998</v>
+        <v>-2.5661</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2182</v>
@@ -1390,13 +1390,13 @@
         <v>0.9792</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9143</v>
+        <v>-0.7806</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2088</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7055</v>
+        <v>-0.5718</v>
       </c>
       <c r="V12" t="n">
         <v>-1.492</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.978500000000002</v>
+        <v>9.978400000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.3415</v>
+        <v>-1.3414</v>
       </c>
       <c r="F13" t="n">
-        <v>11.3196</v>
+        <v>11.3198</v>
       </c>
       <c r="G13" t="n">
         <v>4.1723</v>
@@ -1450,13 +1450,13 @@
         <v>9.187999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.989600000000001</v>
+        <v>-5.9896</v>
       </c>
       <c r="N13" t="n">
         <v>-12.2076</v>
       </c>
       <c r="O13" t="n">
-        <v>6.217999999999999</v>
+        <v>6.218</v>
       </c>
       <c r="P13" t="n">
         <v>8.813000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>26.4395</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2410999999999995</v>
+        <v>-0.2411999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9938999999999999</v>
+        <v>0.9939000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2349</v>
+        <v>-1.235</v>
       </c>
       <c r="V13" t="n">
         <v>-2.7662</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9174</v>
+        <v>2.5498</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9696</v>
+        <v>1.1743</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9477</v>
+        <v>1.3754</v>
       </c>
       <c r="G14" t="n">
         <v>0.4054</v>
@@ -1546,13 +1546,13 @@
         <v>3.1336</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9494</v>
+        <v>-0.317</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2394</v>
+        <v>-0.0347</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.71</v>
+        <v>-0.2823</v>
       </c>
       <c r="V14" t="n">
         <v>2.2655</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GOMEZ LLANES</t>
+          <t>R. ACEVEDO VASQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6914</v>
+        <v>0.7356</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3318</v>
+        <v>2.3198</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0231</v>
+        <v>-1.5842</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1009</v>
+        <v>-0.8138</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9096</v>
+        <v>-0.0215</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8087</v>
+        <v>-0.7924</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5447</v>
+        <v>0.8424</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7679</v>
+        <v>0.7212</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2232</v>
+        <v>0.1212</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4438</v>
+        <v>-1.6563</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1416</v>
+        <v>-0.7427</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5855</v>
+        <v>-0.9136</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7626</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R15" t="n">
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3121</v>
+        <v>-0.3808</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1557</v>
+        <v>0.4899</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1564</v>
+        <v>-0.8707</v>
       </c>
       <c r="V15" t="n">
-        <v>0.041</v>
+        <v>2.7136</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.1152</v>
+        <v>3.9252</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1562</v>
+        <v>-1.2116</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. ACEVEDO VASQUEZ</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5706</v>
+        <v>0.1803</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4221</v>
+        <v>0.1127</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8515</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8138</v>
+        <v>1.3618</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0215</v>
+        <v>2.2906</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7924</v>
+        <v>-0.9288</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8424</v>
+        <v>2.7984</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7212</v>
+        <v>2.1469</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1212</v>
+        <v>0.6515</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6563</v>
+        <v>-1.4365</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7427</v>
+        <v>0.1437</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9136</v>
+        <v>-1.5803</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7834</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1543</v>
+        <v>2.7419</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5458</v>
+        <v>-0.2203</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.0147</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.138</v>
+        <v>-0.2349</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7136</v>
+        <v>0.2138</v>
       </c>
       <c r="W16" t="n">
-        <v>3.9252</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2116</v>
+        <v>-1.0028</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>A. GOMEZ LLANES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.443</v>
+        <v>0.0949</v>
       </c>
       <c r="E17" t="n">
-        <v>0.215</v>
+        <v>-0.7411</v>
       </c>
       <c r="F17" t="n">
-        <v>0.228</v>
+        <v>0.836</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3618</v>
+        <v>1.1009</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2906</v>
+        <v>2.9096</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9288</v>
+        <v>-1.8087</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7984</v>
+        <v>2.5447</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1469</v>
+        <v>2.7679</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6515</v>
+        <v>-0.2232</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4365</v>
+        <v>-1.4438</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1437</v>
+        <v>0.1416</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5803</v>
+        <v>-1.5855</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1751</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q17" t="n">
         <v>-3.917</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7419</v>
+        <v>2.1543</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0425</v>
+        <v>0.7156</v>
       </c>
       <c r="T17" t="n">
-        <v>0.117</v>
+        <v>0.7463</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0746</v>
+        <v>-0.0307</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2138</v>
+        <v>0.041</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2166</v>
+        <v>-0.1152</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0028</v>
+        <v>0.1562</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.32</v>
+        <v>-0.4445</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2277</v>
+        <v>0.023</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5477</v>
+        <v>-0.4675</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1953</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0711</v>
+        <v>-0.0534</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2664</v>
+        <v>0.0618</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1953</v>
+        <v>-0.1151</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0009</v>
+        <v>-1.6171</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0961</v>
+        <v>-1.9768</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.3597</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4195</v>
+        <v>-2.5682</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1712</v>
+        <v>0.2256</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5906</v>
+        <v>-2.7938</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7587</v>
+        <v>-1.8515</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7587</v>
+        <v>0.1548</v>
       </c>
       <c r="L19" t="n">
+        <v>-2.0063</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.7167</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.7875</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.1751</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>-1.1782</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.4125</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-1.5906</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-1.3709</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-2.9377</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3301</v>
+        <v>-0.2905</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4734</v>
+        <v>-0.1253</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8566</v>
+        <v>-0.1653</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5405</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.15</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1401</v>
+        <v>-1.8063</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9771</v>
+        <v>-1.6701</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.163</v>
+        <v>-0.1363</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4518</v>
@@ -2014,13 +2014,13 @@
         <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4509</v>
+        <v>-0.1172</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6534</v>
+        <v>-0.3464</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2025</v>
+        <v>0.2292</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2166</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2403</v>
+        <v>-2.6065</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3861</v>
+        <v>-2.3008</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1459</v>
+        <v>-0.3057</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5682</v>
+        <v>-0.4195</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2256</v>
+        <v>1.1712</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7938</v>
+        <v>-1.5906</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8515</v>
+        <v>0.7587</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1548</v>
+        <v>0.7587</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0063</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7167</v>
+        <v>-1.1782</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0708</v>
+        <v>0.4125</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7875</v>
+        <v>-1.5906</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1751</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9137</v>
+        <v>0.7244</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5346</v>
+        <v>0.2688</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3791</v>
+        <v>0.4557</v>
       </c>
       <c r="V21" t="n">
-        <v>0.06660000000000001</v>
+        <v>-1.5405</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="X21" t="n">
-        <v>0.06660000000000001</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.8995</v>
+        <v>-7.0644</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.363200000000001</v>
+        <v>-8.260899999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4637</v>
+        <v>1.1964</v>
       </c>
       <c r="G22" t="n">
         <v>-1.592</v>
@@ -2170,13 +2170,13 @@
         <v>2.9377</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3452</v>
+        <v>0.1803</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0576</v>
+        <v>0.16</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2876</v>
+        <v>0.0203</v>
       </c>
       <c r="V22" t="n">
         <v>0.2228</v>
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.978400000000001</v>
+        <v>-9.978199999999999</v>
       </c>
       <c r="E23" t="n">
         <v>-11.3199</v>
@@ -2212,7 +2212,7 @@
         <v>1.3414</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.172499999999999</v>
+        <v>-4.1725</v>
       </c>
       <c r="H23" t="n">
         <v>11.2336</v>
@@ -2233,13 +2233,13 @@
         <v>-10.1618</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9740000000000001</v>
+        <v>-0.974</v>
       </c>
       <c r="O23" t="n">
         <v>-9.187900000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-8.813199999999998</v>
+        <v>-8.8132</v>
       </c>
       <c r="Q23" t="n">
         <v>-26.4395</v>
@@ -2248,13 +2248,13 @@
         <v>17.6263</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2412</v>
+        <v>0.2411000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2349</v>
+        <v>1.2351</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9938999999999998</v>
+        <v>-0.9938</v>
       </c>
       <c r="V23" t="n">
         <v>2.7662</v>
@@ -2263,7 +2263,7 @@
         <v>7.8954</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.1292</v>
+        <v>-5.129200000000001</v>
       </c>
     </row>
   </sheetData>
